--- a/data/reina/output/reina_gto.xlsx
+++ b/data/reina/output/reina_gto.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reina ff2f on block SEN 2 (+2) " sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="112 on hit (+9) into SEN" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reina ff2f on block SEN 2 (+2) " sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -484,6 +485,235 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="43" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>112 on hit (+9) into SEN</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Reina1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Reina2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Payoff</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>can also be used for f2,3 on hit into SEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>distribution</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>strategy_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Reina1</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>SEN.2</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>0.6532333645735707</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Reina1</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>SEN.4</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>0.1593252108716026</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Reina1</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>SEN.3+4</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>0.1874414245548266</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Reina2</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>0.4241408176449714</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Reina2</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>DB</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>0.1643236488597313</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Reina2</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>SSL~b</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>0.09762574195563886</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Reina2</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>B~wait</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>0.3139097915396584</v>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/data/reina/output/reina_gto.xlsx
+++ b/data/reina/output/reina_gto.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="112 on hit (+9) into SEN" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reina ff2f on block SEN 2 (+2) " sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="112 on hit (+9) into SEN" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Reina ff2f on block SEN 2 (+2) " sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/reina/output/reina_gto.xlsx
+++ b/data/reina/output/reina_gto.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,9 +36,6 @@
       <sz val="18"/>
     </font>
     <font>
-      <color rgb="007F6000"/>
-    </font>
-    <font>
       <b val="1"/>
       <color rgb="00333333"/>
       <sz val="12"/>
@@ -52,8 +49,20 @@
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
+    <font>
+      <color rgb="00006100"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="FF9C0006"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="007F6000"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -62,14 +71,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
+        <fgColor rgb="004F81BD"/>
+        <bgColor rgb="004F81BD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004F81BD"/>
-        <bgColor rgb="004F81BD"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -101,31 +122,37 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -497,7 +524,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
@@ -530,7 +557,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Reina2</t>
         </is>
@@ -542,7 +569,7 @@
           <t>Payoff</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="6" t="n">
         <v>5.2</v>
       </c>
     </row>
@@ -552,7 +579,7 @@
           <t>Comment</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>can also be used for f2,3 on hit into SEN</t>
         </is>
@@ -561,150 +588,150 @@
     <row r="6"/>
     <row r="7"/>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>strategy</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>distribution</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>strategy_value</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>Reina1</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Reina1</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>SEN.2</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="10" t="n">
         <v>0.6532333645735707</v>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="D9" s="4" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Reina1</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Reina1</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>SEN.4</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="10" t="n">
         <v>0.1593252108716026</v>
       </c>
-      <c r="D10" s="8" t="n">
+      <c r="D10" s="4" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>Reina1</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Reina1</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>SEN.3+4</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="10" t="n">
         <v>0.1874414245548266</v>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="D11" s="4" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>Reina2</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Reina2</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" s="11" t="n">
         <v>0.4241408176449714</v>
       </c>
-      <c r="D12" s="8" t="n">
+      <c r="D12" s="5" t="n">
         <v>-5</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Reina2</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Reina2</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C13" s="11" t="n">
         <v>0.1643236488597313</v>
       </c>
-      <c r="D13" s="8" t="n">
+      <c r="D13" s="5" t="n">
         <v>-5</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>Reina2</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Reina2</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>SSL~b</t>
         </is>
       </c>
-      <c r="C14" s="9" t="n">
+      <c r="C14" s="11" t="n">
         <v>0.09762574195563886</v>
       </c>
-      <c r="D14" s="8" t="n">
+      <c r="D14" s="5" t="n">
         <v>-5</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>Reina2</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Reina2</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>B~wait</t>
         </is>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="11" t="n">
         <v>0.3139097915396584</v>
       </c>
-      <c r="D15" s="8" t="n">
+      <c r="D15" s="5" t="n">
         <v>-5</v>
       </c>
     </row>
@@ -726,7 +753,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="65" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
@@ -759,7 +786,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Reina2</t>
         </is>
@@ -771,7 +798,7 @@
           <t>Payoff</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="6" t="n">
         <v>7</v>
       </c>
     </row>
@@ -781,7 +808,7 @@
           <t>Comment</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Mixup after Reina's WGS.DF+4,2,D on hit into WRA, in the mirror</t>
         </is>
@@ -790,186 +817,186 @@
     <row r="6"/>
     <row r="7"/>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>strategy</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>distribution</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>strategy_value</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>Reina1</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Reina1</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>WRA.2</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="10" t="n">
         <v>0.2282866725642315</v>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="D9" s="4" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Reina1</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Reina1</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>WRA.1+2</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="10" t="n">
         <v>0.02703371968361435</v>
       </c>
-      <c r="D10" s="8" t="n">
+      <c r="D10" s="4" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>Reina1</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Reina1</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>WRA.3+4</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="10" t="n">
         <v>0.4546212473176012</v>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="D11" s="4" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>Reina1</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Reina1</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>WRA.d+4</t>
         </is>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" s="10" t="n">
         <v>0.290058360434553</v>
       </c>
-      <c r="D12" s="8" t="n">
+      <c r="D12" s="4" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Reina2</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Reina2</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>b,B~punish</t>
         </is>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C13" s="11" t="n">
         <v>0.2201072132495159</v>
       </c>
-      <c r="D13" s="8" t="n">
+      <c r="D13" s="5" t="n">
         <v>-7</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>Reina2</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Reina2</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>DB~punish</t>
         </is>
       </c>
-      <c r="C14" s="9" t="n">
+      <c r="C14" s="11" t="n">
         <v>0.1067844945345311</v>
       </c>
-      <c r="D14" s="8" t="n">
+      <c r="D14" s="5" t="n">
         <v>-7</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>Reina2</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Reina2</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>jab</t>
         </is>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="11" t="n">
         <v>0.3361455730367502</v>
       </c>
-      <c r="D15" s="8" t="n">
+      <c r="D15" s="5" t="n">
         <v>-7</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>Reina2</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Reina2</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>SSR~b</t>
         </is>
       </c>
-      <c r="C16" s="9" t="n">
+      <c r="C16" s="11" t="n">
         <v>0.1532876995273655</v>
       </c>
-      <c r="D16" s="8" t="n">
+      <c r="D16" s="5" t="n">
         <v>-7</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>Reina2</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Reina2</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>b,B~wait</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="C17" s="11" t="n">
         <v>0.1836750196518372</v>
       </c>
-      <c r="D17" s="8" t="n">
+      <c r="D17" s="5" t="n">
         <v>-7</v>
       </c>
     </row>
@@ -991,7 +1018,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="54" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
@@ -1024,7 +1051,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Reina2</t>
         </is>
@@ -1036,7 +1063,7 @@
           <t>Payoff</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="6" t="n">
         <v>-6.3</v>
       </c>
     </row>
@@ -1046,7 +1073,7 @@
           <t>Comment</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>The ubiquitous f,F+2,F mixup on block, in the mirror</t>
         </is>
@@ -1055,204 +1082,204 @@
     <row r="6"/>
     <row r="7"/>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>strategy</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>distribution</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>strategy_value</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>Reina1</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Reina1</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>SEN.3</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="10" t="n">
         <v>0.3586049920859399</v>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="D9" s="4" t="n">
         <v>-6</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Reina1</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Reina1</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>SEN.2</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="10" t="n">
         <v>0.3611889476142205</v>
       </c>
-      <c r="D10" s="8" t="n">
+      <c r="D10" s="4" t="n">
         <v>-6</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>Reina1</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Reina1</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>SEN.1</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="10" t="n">
         <v>0.04251022196210444</v>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="D11" s="4" t="n">
         <v>-6</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>Reina1</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Reina1</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>SEN.1,qcf+2</t>
         </is>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" s="10" t="n">
         <v>0.01774698586767467</v>
       </c>
-      <c r="D12" s="8" t="n">
+      <c r="D12" s="4" t="n">
         <v>-6</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Reina1</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Reina1</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>SEN.1+2</t>
         </is>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C13" s="10" t="n">
         <v>0.2199488524700604</v>
       </c>
-      <c r="D13" s="8" t="n">
+      <c r="D13" s="4" t="n">
         <v>-6</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>Reina2</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Reina2</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="C14" s="9" t="n">
+      <c r="C14" s="11" t="n">
         <v>0.2816370938337376</v>
       </c>
-      <c r="D14" s="8" t="n">
+      <c r="D14" s="5" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>Reina2</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Reina2</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>112</t>
         </is>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="11" t="n">
         <v>0.3407855228584662</v>
       </c>
-      <c r="D15" s="8" t="n">
+      <c r="D15" s="5" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>Reina2</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Reina2</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>SSL~b~punish</t>
         </is>
       </c>
-      <c r="C16" s="9" t="n">
+      <c r="C16" s="11" t="n">
         <v>0.01052145697734052</v>
       </c>
-      <c r="D16" s="8" t="n">
+      <c r="D16" s="5" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>Reina2</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Reina2</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>SSR~b~punish</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="C17" s="11" t="n">
         <v>0.2478366564612363</v>
       </c>
-      <c r="D17" s="8" t="n">
+      <c r="D17" s="5" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>Reina2</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Reina2</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>SSL~b~wait</t>
         </is>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="C18" s="11" t="n">
         <v>0.1192192698692193</v>
       </c>
-      <c r="D18" s="8" t="n">
+      <c r="D18" s="5" t="n">
         <v>6</v>
       </c>
     </row>
